--- a/COMPSYS704_Project1_Interface_V1.xlsx
+++ b/COMPSYS704_Project1_Interface_V1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interfaces" sheetId="1" r:id="R1b965130a7934c5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interfaces" sheetId="1" r:id="R6f4efe53ea8943c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -62,7 +62,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -77,6 +77,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF000000"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9D9D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -223,7 +243,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="73">
+  <x:cellXfs count="136">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -421,6 +441,177 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -626,41 +817,41 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14"/>
   <x:cols>
-    <x:col min="1" max="1" width="25.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="29.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="27.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="31.25" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="33.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="35" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="2.75" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="51.25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="53.75" hidden="0" customWidth="1"/>
     <x:col min="9" max="10" width="4" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25.5" customHeight="1">
-      <x:c r="A1" s="59" t="str">
+      <x:c r="A1" s="123" t="str">
         <x:v>COMPSYS704 Project 1 — Interface V1</x:v>
       </x:c>
-      <x:c r="B1" s="60"/>
-      <x:c r="C1" s="60"/>
-      <x:c r="D1" s="60"/>
-      <x:c r="E1" s="61"/>
+      <x:c r="B1" s="124"/>
+      <x:c r="C1" s="124"/>
+      <x:c r="D1" s="124"/>
+      <x:c r="E1" s="125"/>
       <x:c r="F1" s="62"/>
-      <x:c r="G1" s="63" t="str">
+      <x:c r="G1" s="126" t="str">
         <x:v>Integration Notes</x:v>
       </x:c>
-      <x:c r="H1" s="64"/>
+      <x:c r="H1" s="127"/>
       <x:c r="I1"/>
       <x:c r="J1"/>
     </x:row>
-    <x:row r="2" ht="19.5" customHeight="1">
-      <x:c r="A2" s="65" t="str">
-        <x:v>Integration quick reference • Tested SystemJ declarations, XML mappings and V1 documents</x:v>
-      </x:c>
-      <x:c r="B2" s="66"/>
-      <x:c r="C2" s="66"/>
-      <x:c r="D2" s="66"/>
-      <x:c r="E2" s="67"/>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" s="128" t="str">
+        <x:v>Brief-aligned Coordinator interface • 8 Machine Controllers • Integration quick reference</x:v>
+      </x:c>
+      <x:c r="B2" s="129"/>
+      <x:c r="C2" s="129"/>
+      <x:c r="D2" s="129"/>
+      <x:c r="E2" s="130"/>
       <x:c r="F2" s="62"/>
       <x:c r="G2" s="62"/>
       <x:c r="H2" s="62"/>
@@ -674,97 +865,97 @@
       <x:c r="D3" s="62"/>
       <x:c r="E3" s="62"/>
       <x:c r="F3" s="62"/>
-      <x:c r="G3" s="68" t="str">
+      <x:c r="G3" s="131" t="str">
         <x:v>V1 Team Freeze</x:v>
       </x:c>
-      <x:c r="H3" s="69"/>
+      <x:c r="H3" s="132"/>
       <x:c r="I3"/>
       <x:c r="J3"/>
     </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="70" t="str">
+    <x:row r="4" ht="31.5" customHeight="1">
+      <x:c r="A4" s="133" t="str">
         <x:v>1. POS / Coordinator</x:v>
       </x:c>
-      <x:c r="B4" s="71"/>
-      <x:c r="C4" s="71"/>
-      <x:c r="D4" s="71"/>
-      <x:c r="E4" s="72"/>
+      <x:c r="B4" s="134"/>
+      <x:c r="C4" s="134"/>
+      <x:c r="D4" s="134"/>
+      <x:c r="E4" s="135"/>
       <x:c r="F4" s="62"/>
-      <x:c r="G4" s="54" t="str">
+      <x:c r="G4" s="118" t="str">
         <x:v>Rule</x:v>
       </x:c>
-      <x:c r="H4" s="55" t="str">
+      <x:c r="H4" s="119" t="str">
         <x:v>Do not rename signals, change types/status codes/ports, or add Coordinator Plant-control signals without group agreement.</x:v>
       </x:c>
       <x:c r="I4"/>
       <x:c r="J4"/>
     </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="40" t="str">
+    <x:row r="5" ht="31.5" customHeight="1">
+      <x:c r="A5" s="104" t="str">
         <x:v>Signal</x:v>
       </x:c>
-      <x:c r="B5" s="40" t="str">
+      <x:c r="B5" s="104" t="str">
         <x:v>Direction</x:v>
       </x:c>
-      <x:c r="C5" s="40" t="str">
+      <x:c r="C5" s="104" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D5" s="40" t="str">
+      <x:c r="D5" s="104" t="str">
         <x:v>Receiver Port</x:v>
       </x:c>
-      <x:c r="E5" s="40" t="str">
+      <x:c r="E5" s="104" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="F5" s="62"/>
-      <x:c r="G5" s="54" t="str">
+      <x:c r="G5" s="118" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="H5" s="55" t="str">
-        <x:v>This is the team-agreed Integration V1 baseline, not a forever-immutable API.</x:v>
+      <x:c r="H5" s="119" t="str">
+        <x:v>Team-agreed Integration V1 baseline; it is not a forever-immutable API.</x:v>
       </x:c>
       <x:c r="I5"/>
       <x:c r="J5"/>
     </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="41" t="str">
+    <x:row r="6" ht="31.5" customHeight="1">
+      <x:c r="A6" s="105" t="str">
         <x:v>ORDER</x:v>
       </x:c>
-      <x:c r="B6" s="41" t="str">
+      <x:c r="B6" s="105" t="str">
         <x:v>POS → Coordinator</x:v>
       </x:c>
-      <x:c r="C6" s="41" t="str">
+      <x:c r="C6" s="105" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="D6" s="42" t="n">
+      <x:c r="D6" s="106" t="n">
         <x:v>11001</x:v>
       </x:c>
-      <x:c r="E6" s="41" t="str">
+      <x:c r="E6" s="105" t="str">
         <x:v>Submit validated order payload</x:v>
       </x:c>
       <x:c r="F6" s="62"/>
-      <x:c r="G6" s="54" t="str">
+      <x:c r="G6" s="118" t="str">
         <x:v>Authority</x:v>
       </x:c>
-      <x:c r="H6" s="55" t="str">
-        <x:v>Tested .sysj/XML and V1 interface documents are the source of truth.</x:v>
+      <x:c r="H6" s="119" t="str">
+        <x:v>Tested .sysj/XML plus the V1 interface documents are the source of truth.</x:v>
       </x:c>
       <x:c r="I6"/>
       <x:c r="J6"/>
     </x:row>
     <x:row r="7" ht="17.25" customHeight="1">
-      <x:c r="A7" s="41" t="str">
+      <x:c r="A7" s="105" t="str">
         <x:v>ORDER_COMPLETE</x:v>
       </x:c>
-      <x:c r="B7" s="41" t="str">
+      <x:c r="B7" s="105" t="str">
         <x:v>Coordinator → POS</x:v>
       </x:c>
-      <x:c r="C7" s="41" t="str">
+      <x:c r="C7" s="105" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="D7" s="42" t="n">
+      <x:c r="D7" s="106" t="n">
         <x:v>11000</x:v>
       </x:c>
-      <x:c r="E7" s="41" t="str">
+      <x:c r="E7" s="105" t="str">
         <x:v>Report full order completed</x:v>
       </x:c>
       <x:c r="F7" s="62"/>
@@ -780,608 +971,620 @@
       <x:c r="D8" s="62"/>
       <x:c r="E8" s="62"/>
       <x:c r="F8" s="62"/>
-      <x:c r="G8" s="68" t="str">
-        <x:v>Protocol Notes</x:v>
-      </x:c>
-      <x:c r="H8" s="69"/>
+      <x:c r="G8" s="131" t="str">
+        <x:v>Design Basis</x:v>
+      </x:c>
+      <x:c r="H8" s="132"/>
       <x:c r="I8"/>
       <x:c r="J8"/>
     </x:row>
-    <x:row r="9" ht="28.5" customHeight="1">
-      <x:c r="A9" s="70" t="str">
-        <x:v>2. Bottle Loader</x:v>
-      </x:c>
-      <x:c r="B9" s="71"/>
-      <x:c r="C9" s="71"/>
-      <x:c r="D9" s="71"/>
-      <x:c r="E9" s="72"/>
+    <x:row r="9" ht="39" customHeight="1">
+      <x:c r="A9" s="133" t="str">
+        <x:v>2. Bottle Loader Controller</x:v>
+      </x:c>
+      <x:c r="B9" s="134"/>
+      <x:c r="C9" s="134"/>
+      <x:c r="D9" s="134"/>
+      <x:c r="E9" s="135"/>
       <x:c r="F9" s="62"/>
-      <x:c r="G9" s="54" t="str">
-        <x:v>Receiver rule</x:v>
-      </x:c>
-      <x:c r="H9" s="55" t="str">
-        <x:v>The port belongs to the receiving SystemJ runtime; production uses 127.0.0.1.</x:v>
+      <x:c r="G9" s="118" t="str">
+        <x:v>2026 brief</x:v>
+      </x:c>
+      <x:c r="H9" s="119" t="str">
+        <x:v>Separate Conveyor, Rotary Turntable, Filler and Capper clock-domains; include Bottle Loader, Lid Loader and Bottle Unloader.</x:v>
       </x:c>
       <x:c r="I9"/>
       <x:c r="J9"/>
     </x:row>
-    <x:row r="10" ht="28.5" customHeight="1">
-      <x:c r="A10" s="40" t="str">
+    <x:row r="10" ht="39" customHeight="1">
+      <x:c r="A10" s="104" t="str">
         <x:v>Signal</x:v>
       </x:c>
-      <x:c r="B10" s="40" t="str">
+      <x:c r="B10" s="104" t="str">
         <x:v>Direction</x:v>
       </x:c>
-      <x:c r="C10" s="40" t="str">
+      <x:c r="C10" s="104" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D10" s="40" t="str">
+      <x:c r="D10" s="104" t="str">
         <x:v>Receiver Port</x:v>
       </x:c>
-      <x:c r="E10" s="40" t="str">
+      <x:c r="E10" s="104" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="F10" s="62"/>
-      <x:c r="G10" s="54" t="str">
-        <x:v>ORDER</x:v>
-      </x:c>
-      <x:c r="H10" s="55" t="str">
-        <x:v>orderId|productCount|productId,A%,B%,quantity;...</x:v>
+      <x:c r="G10" s="118" t="str">
+        <x:v>Team decision</x:v>
+      </x:c>
+      <x:c r="H10" s="119" t="str">
+        <x:v>Keep Filler A and Filler B as two logical Controllers for the required two-liquid mix.</x:v>
       </x:c>
       <x:c r="I10"/>
       <x:c r="J10"/>
     </x:row>
-    <x:row r="11" ht="28.5" customHeight="1">
-      <x:c r="A11" s="41" t="str">
+    <x:row r="11" ht="39" customHeight="1">
+      <x:c r="A11" s="105" t="str">
         <x:v>START_ORDER</x:v>
       </x:c>
-      <x:c r="B11" s="41" t="str">
+      <x:c r="B11" s="105" t="str">
         <x:v>Coordinator → Bottle Loader</x:v>
       </x:c>
-      <x:c r="C11" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D11" s="42" t="n">
+      <x:c r="C11" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D11" s="106" t="n">
         <x:v>11002</x:v>
       </x:c>
-      <x:c r="E11" s="41" t="str">
+      <x:c r="E11" s="105" t="str">
         <x:v>Start current batch (quantity)</x:v>
       </x:c>
       <x:c r="F11" s="62"/>
-      <x:c r="G11" s="54" t="str">
-        <x:v>ORDER_COMPLETE</x:v>
-      </x:c>
-      <x:c r="H11" s="55" t="str">
-        <x:v>orderId|COMPLETED|completionTimeSeconds</x:v>
+      <x:c r="G11" s="118" t="str">
+        <x:v>Boundary</x:v>
+      </x:c>
+      <x:c r="H11" s="119" t="str">
+        <x:v>Coordinator handles orders, recipes, status and completion only; Plant signals stay inside machine modules.</x:v>
       </x:c>
       <x:c r="I11"/>
       <x:c r="J11"/>
     </x:row>
-    <x:row r="12" ht="28.5" customHeight="1">
-      <x:c r="A12" s="41" t="str">
+    <x:row r="12" ht="39" customHeight="1">
+      <x:c r="A12" s="105" t="str">
         <x:v>LOADER_STATUS_REQUEST</x:v>
       </x:c>
-      <x:c r="B12" s="41" t="str">
+      <x:c r="B12" s="105" t="str">
         <x:v>Coordinator → Bottle Loader</x:v>
       </x:c>
-      <x:c r="C12" s="41" t="str">
+      <x:c r="C12" s="105" t="str">
         <x:v>pure signal</x:v>
       </x:c>
-      <x:c r="D12" s="42" t="n">
+      <x:c r="D12" s="106" t="n">
         <x:v>11002</x:v>
       </x:c>
-      <x:c r="E12" s="41" t="str">
+      <x:c r="E12" s="105" t="str">
         <x:v>Request current status</x:v>
       </x:c>
       <x:c r="F12" s="62"/>
-      <x:c r="G12" s="54" t="str">
-        <x:v>Batch start</x:v>
-      </x:c>
-      <x:c r="H12" s="55" t="str">
-        <x:v>START_ORDER is quantity-valued and emitted once per product batch, not once per bottle.</x:v>
+      <x:c r="G12" s="118" t="str">
+        <x:v>Completion</x:v>
+      </x:c>
+      <x:c r="H12" s="119" t="str">
+        <x:v>BOTTLE_DONE is sent by Bottle Unloader after collection, not by Capper.</x:v>
       </x:c>
       <x:c r="I12"/>
       <x:c r="J12"/>
     </x:row>
-    <x:row r="13" ht="28.5" customHeight="1">
-      <x:c r="A13" s="41" t="str">
+    <x:row r="13" ht="17.25" customHeight="1">
+      <x:c r="A13" s="105" t="str">
         <x:v>LOADER_STATUS</x:v>
       </x:c>
-      <x:c r="B13" s="41" t="str">
+      <x:c r="B13" s="105" t="str">
         <x:v>Bottle Loader → Coordinator</x:v>
       </x:c>
-      <x:c r="C13" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D13" s="42" t="n">
+      <x:c r="C13" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D13" s="106" t="n">
         <x:v>11001</x:v>
       </x:c>
-      <x:c r="E13" s="41" t="str">
+      <x:c r="E13" s="105" t="str">
         <x:v>Return current status code</x:v>
       </x:c>
       <x:c r="F13" s="62"/>
-      <x:c r="G13" s="54" t="str">
-        <x:v>Bottle completion</x:v>
-      </x:c>
-      <x:c r="H13" s="55" t="str">
-        <x:v>BOTTLE_DONE means one bottle completed the full line; it is not whole-order completion.</x:v>
-      </x:c>
+      <x:c r="G13" s="62"/>
+      <x:c r="H13" s="62"/>
       <x:c r="I13"/>
       <x:c r="J13"/>
     </x:row>
-    <x:row r="14" ht="28.5" customHeight="1">
+    <x:row r="14" ht="17.25" customHeight="1">
       <x:c r="A14" s="62"/>
       <x:c r="B14" s="62"/>
       <x:c r="C14" s="62"/>
       <x:c r="D14" s="62"/>
       <x:c r="E14" s="62"/>
       <x:c r="F14" s="62"/>
-      <x:c r="G14" s="54" t="str">
-        <x:v>Visualisation</x:v>
-      </x:c>
-      <x:c r="H14" s="55" t="str">
-        <x:v>All VIZ_* signals go only to ABSVisualisationPlantCD at 127.0.0.1:11008.</x:v>
-      </x:c>
+      <x:c r="G14" s="131" t="str">
+        <x:v>Protocol Notes</x:v>
+      </x:c>
+      <x:c r="H14" s="132"/>
       <x:c r="I14"/>
       <x:c r="J14"/>
     </x:row>
-    <x:row r="15" ht="28.5" customHeight="1">
-      <x:c r="A15" s="70" t="str">
-        <x:v>3. Transport</x:v>
-      </x:c>
-      <x:c r="B15" s="71"/>
-      <x:c r="C15" s="71"/>
-      <x:c r="D15" s="71"/>
-      <x:c r="E15" s="72"/>
+    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="A15" s="133" t="str">
+        <x:v>3. Conveyor Controller</x:v>
+      </x:c>
+      <x:c r="B15" s="134"/>
+      <x:c r="C15" s="134"/>
+      <x:c r="D15" s="134"/>
+      <x:c r="E15" s="135"/>
       <x:c r="F15" s="62"/>
-      <x:c r="G15" s="54" t="str">
-        <x:v>WAITING</x:v>
-      </x:c>
-      <x:c r="H15" s="55" t="str">
-        <x:v>GUI initial label only; it is not status code 5.</x:v>
+      <x:c r="G15" s="118" t="str">
+        <x:v>Receiver rule</x:v>
+      </x:c>
+      <x:c r="H15" s="119" t="str">
+        <x:v>The port belongs to the receiving SystemJ runtime; production uses 127.0.0.1.</x:v>
       </x:c>
       <x:c r="I15"/>
       <x:c r="J15"/>
     </x:row>
-    <x:row r="16" ht="17.25" customHeight="1">
-      <x:c r="A16" s="40" t="str">
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="104" t="str">
         <x:v>Signal</x:v>
       </x:c>
-      <x:c r="B16" s="40" t="str">
+      <x:c r="B16" s="104" t="str">
         <x:v>Direction</x:v>
       </x:c>
-      <x:c r="C16" s="40" t="str">
+      <x:c r="C16" s="104" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D16" s="40" t="str">
+      <x:c r="D16" s="104" t="str">
         <x:v>Receiver Port</x:v>
       </x:c>
-      <x:c r="E16" s="40" t="str">
+      <x:c r="E16" s="104" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="F16" s="62"/>
-      <x:c r="G16" s="62"/>
-      <x:c r="H16" s="62"/>
+      <x:c r="G16" s="118" t="str">
+        <x:v>ORDER</x:v>
+      </x:c>
+      <x:c r="H16" s="119" t="str">
+        <x:v>orderId|productCount|productId,A%,B%,quantity;...</x:v>
+      </x:c>
       <x:c r="I16"/>
       <x:c r="J16"/>
     </x:row>
-    <x:row r="17" ht="17.25" customHeight="1">
-      <x:c r="A17" s="41" t="str">
-        <x:v>TRANSPORT_STATUS_REQUEST</x:v>
-      </x:c>
-      <x:c r="B17" s="41" t="str">
-        <x:v>Coordinator → Transport</x:v>
-      </x:c>
-      <x:c r="C17" s="41" t="str">
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="105" t="str">
+        <x:v>CONVEYOR_STATUS_REQUEST</x:v>
+      </x:c>
+      <x:c r="B17" s="105" t="str">
+        <x:v>Coordinator → Conveyor</x:v>
+      </x:c>
+      <x:c r="C17" s="105" t="str">
         <x:v>pure signal</x:v>
       </x:c>
-      <x:c r="D17" s="42" t="n">
+      <x:c r="D17" s="106" t="n">
         <x:v>11003</x:v>
       </x:c>
-      <x:c r="E17" s="41" t="str">
+      <x:c r="E17" s="105" t="str">
         <x:v>Request current status</x:v>
       </x:c>
       <x:c r="F17" s="62"/>
-      <x:c r="G17" s="68" t="str">
-        <x:v>Production Receiver Map</x:v>
-      </x:c>
-      <x:c r="H17" s="69"/>
+      <x:c r="G17" s="118" t="str">
+        <x:v>ORDER_COMPLETE</x:v>
+      </x:c>
+      <x:c r="H17" s="119" t="str">
+        <x:v>orderId|COMPLETED|completionTimeSeconds</x:v>
+      </x:c>
       <x:c r="I17"/>
       <x:c r="J17"/>
     </x:row>
-    <x:row r="18" ht="17.25" customHeight="1">
-      <x:c r="A18" s="41" t="str">
-        <x:v>TRANSPORT_STATUS</x:v>
-      </x:c>
-      <x:c r="B18" s="41" t="str">
-        <x:v>Transport → Coordinator</x:v>
-      </x:c>
-      <x:c r="C18" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D18" s="42" t="n">
+    <x:row r="18" ht="30" customHeight="1">
+      <x:c r="A18" s="105" t="str">
+        <x:v>CONVEYOR_STATUS</x:v>
+      </x:c>
+      <x:c r="B18" s="105" t="str">
+        <x:v>Conveyor → Coordinator</x:v>
+      </x:c>
+      <x:c r="C18" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D18" s="106" t="n">
         <x:v>11001</x:v>
       </x:c>
-      <x:c r="E18" s="41" t="str">
+      <x:c r="E18" s="105" t="str">
         <x:v>Return current status code</x:v>
       </x:c>
       <x:c r="F18" s="62"/>
-      <x:c r="G18" s="40" t="str">
-        <x:v>Component</x:v>
-      </x:c>
-      <x:c r="H18" s="40" t="str">
-        <x:v>Clock Domain @ IP:Port</x:v>
+      <x:c r="G18" s="118" t="str">
+        <x:v>Batch start</x:v>
+      </x:c>
+      <x:c r="H18" s="119" t="str">
+        <x:v>START_ORDER is quantity-valued and emitted once per product batch.</x:v>
       </x:c>
       <x:c r="I18"/>
       <x:c r="J18"/>
     </x:row>
-    <x:row r="19" ht="17.25" customHeight="1">
+    <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="62"/>
       <x:c r="B19" s="62"/>
       <x:c r="C19" s="62"/>
       <x:c r="D19" s="62"/>
       <x:c r="E19" s="62"/>
       <x:c r="F19" s="62"/>
-      <x:c r="G19" s="54" t="str">
-        <x:v>POS</x:v>
-      </x:c>
-      <x:c r="H19" s="55" t="str">
-        <x:v>POSCD @ 127.0.0.1:11000</x:v>
+      <x:c r="G19" s="118" t="str">
+        <x:v>Bottle completion</x:v>
+      </x:c>
+      <x:c r="H19" s="119" t="str">
+        <x:v>One BOTTLE_DONE = one finished bottle collected by Bottle Unloader.</x:v>
       </x:c>
       <x:c r="I19"/>
       <x:c r="J19"/>
     </x:row>
-    <x:row r="20" ht="17.25" customHeight="1">
-      <x:c r="A20" s="70" t="str">
-        <x:v>4. Filler A</x:v>
-      </x:c>
-      <x:c r="B20" s="71"/>
-      <x:c r="C20" s="71"/>
-      <x:c r="D20" s="71"/>
-      <x:c r="E20" s="72"/>
+    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="A20" s="133" t="str">
+        <x:v>4. Rotary Turntable Controller</x:v>
+      </x:c>
+      <x:c r="B20" s="134"/>
+      <x:c r="C20" s="134"/>
+      <x:c r="D20" s="134"/>
+      <x:c r="E20" s="135"/>
       <x:c r="F20" s="62"/>
-      <x:c r="G20" s="54" t="str">
-        <x:v>ABS Coordinator</x:v>
-      </x:c>
-      <x:c r="H20" s="55" t="str">
-        <x:v>CoordinatorCD @ 127.0.0.1:11001</x:v>
+      <x:c r="G20" s="118" t="str">
+        <x:v>Visualisation</x:v>
+      </x:c>
+      <x:c r="H20" s="119" t="str">
+        <x:v>All VIZ_* signals go to ABSVisualisationPlantCD at 127.0.0.1:11008.</x:v>
       </x:c>
       <x:c r="I20"/>
       <x:c r="J20"/>
     </x:row>
-    <x:row r="21" ht="17.25" customHeight="1">
-      <x:c r="A21" s="40" t="str">
+    <x:row r="21" ht="30" customHeight="1">
+      <x:c r="A21" s="104" t="str">
         <x:v>Signal</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="str">
+      <x:c r="B21" s="104" t="str">
         <x:v>Direction</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="str">
+      <x:c r="C21" s="104" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="str">
+      <x:c r="D21" s="104" t="str">
         <x:v>Receiver Port</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="str">
+      <x:c r="E21" s="104" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="F21" s="62"/>
-      <x:c r="G21" s="54" t="str">
-        <x:v>Bottle Loader</x:v>
-      </x:c>
-      <x:c r="H21" s="55" t="str">
-        <x:v>BottleLoaderControllerCD @ 127.0.0.1:11002</x:v>
+      <x:c r="G21" s="118" t="str">
+        <x:v>WAITING</x:v>
+      </x:c>
+      <x:c r="H21" s="119" t="str">
+        <x:v>GUI initial label only; it is not status code 5.</x:v>
       </x:c>
       <x:c r="I21"/>
       <x:c r="J21"/>
     </x:row>
     <x:row r="22" ht="17.25" customHeight="1">
-      <x:c r="A22" s="41" t="str">
-        <x:v>FILL_A_RATIO</x:v>
-      </x:c>
-      <x:c r="B22" s="41" t="str">
-        <x:v>Coordinator → Filler A</x:v>
-      </x:c>
-      <x:c r="C22" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D22" s="42" t="n">
-        <x:v>11004</x:v>
-      </x:c>
-      <x:c r="E22" s="41" t="str">
-        <x:v>Set Liquid A percentage (0–100)</x:v>
+      <x:c r="A22" s="105" t="str">
+        <x:v>ROTARY_STATUS_REQUEST</x:v>
+      </x:c>
+      <x:c r="B22" s="105" t="str">
+        <x:v>Coordinator → Rotary Turntable</x:v>
+      </x:c>
+      <x:c r="C22" s="105" t="str">
+        <x:v>pure signal</x:v>
+      </x:c>
+      <x:c r="D22" s="106" t="n">
+        <x:v>11009</x:v>
+      </x:c>
+      <x:c r="E22" s="105" t="str">
+        <x:v>Request current status</x:v>
       </x:c>
       <x:c r="F22" s="62"/>
-      <x:c r="G22" s="54" t="str">
-        <x:v>Transport</x:v>
-      </x:c>
-      <x:c r="H22" s="55" t="str">
-        <x:v>TransportControllerCD @ 127.0.0.1:11003</x:v>
-      </x:c>
+      <x:c r="G22" s="62"/>
+      <x:c r="H22" s="62"/>
       <x:c r="I22"/>
       <x:c r="J22"/>
     </x:row>
     <x:row r="23" ht="17.25" customHeight="1">
-      <x:c r="A23" s="41" t="str">
-        <x:v>FILLER_A_STATUS_REQUEST</x:v>
-      </x:c>
-      <x:c r="B23" s="41" t="str">
-        <x:v>Coordinator → Filler A</x:v>
-      </x:c>
-      <x:c r="C23" s="41" t="str">
-        <x:v>pure signal</x:v>
-      </x:c>
-      <x:c r="D23" s="42" t="n">
-        <x:v>11004</x:v>
-      </x:c>
-      <x:c r="E23" s="41" t="str">
-        <x:v>Request current status</x:v>
+      <x:c r="A23" s="105" t="str">
+        <x:v>ROTARY_STATUS</x:v>
+      </x:c>
+      <x:c r="B23" s="105" t="str">
+        <x:v>Rotary Turntable → Coordinator</x:v>
+      </x:c>
+      <x:c r="C23" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D23" s="106" t="n">
+        <x:v>11001</x:v>
+      </x:c>
+      <x:c r="E23" s="105" t="str">
+        <x:v>Return current status code</x:v>
       </x:c>
       <x:c r="F23" s="62"/>
-      <x:c r="G23" s="54" t="str">
-        <x:v>Filler A</x:v>
-      </x:c>
-      <x:c r="H23" s="55" t="str">
-        <x:v>FillerAControllerCD @ 127.0.0.1:11004</x:v>
-      </x:c>
+      <x:c r="G23" s="131" t="str">
+        <x:v>Production Receiver Map</x:v>
+      </x:c>
+      <x:c r="H23" s="132"/>
       <x:c r="I23"/>
       <x:c r="J23"/>
     </x:row>
     <x:row r="24" ht="17.25" customHeight="1">
-      <x:c r="A24" s="41" t="str">
-        <x:v>FILLER_A_STATUS</x:v>
-      </x:c>
-      <x:c r="B24" s="41" t="str">
-        <x:v>Filler A → Coordinator</x:v>
-      </x:c>
-      <x:c r="C24" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D24" s="42" t="n">
-        <x:v>11001</x:v>
-      </x:c>
-      <x:c r="E24" s="41" t="str">
-        <x:v>Return current status code</x:v>
-      </x:c>
+      <x:c r="A24" s="62"/>
+      <x:c r="B24" s="62"/>
+      <x:c r="C24" s="62"/>
+      <x:c r="D24" s="62"/>
+      <x:c r="E24" s="62"/>
       <x:c r="F24" s="62"/>
-      <x:c r="G24" s="54" t="str">
-        <x:v>Filler B</x:v>
-      </x:c>
-      <x:c r="H24" s="55" t="str">
-        <x:v>FillerBControllerCD @ 127.0.0.1:11005</x:v>
+      <x:c r="G24" s="104" t="str">
+        <x:v>Component</x:v>
+      </x:c>
+      <x:c r="H24" s="104" t="str">
+        <x:v>Clock Domain @ IP:Port</x:v>
       </x:c>
       <x:c r="I24"/>
       <x:c r="J24"/>
     </x:row>
     <x:row r="25" ht="17.25" customHeight="1">
-      <x:c r="A25" s="62"/>
-      <x:c r="B25" s="62"/>
-      <x:c r="C25" s="62"/>
-      <x:c r="D25" s="62"/>
-      <x:c r="E25" s="62"/>
+      <x:c r="A25" s="133" t="str">
+        <x:v>5. Filler A Controller</x:v>
+      </x:c>
+      <x:c r="B25" s="134"/>
+      <x:c r="C25" s="134"/>
+      <x:c r="D25" s="134"/>
+      <x:c r="E25" s="135"/>
       <x:c r="F25" s="62"/>
-      <x:c r="G25" s="54" t="str">
-        <x:v>Lid Loader</x:v>
-      </x:c>
-      <x:c r="H25" s="55" t="str">
-        <x:v>LidLoaderControllerCD @ 127.0.0.1:11006</x:v>
+      <x:c r="G25" s="118" t="str">
+        <x:v>POS</x:v>
+      </x:c>
+      <x:c r="H25" s="119" t="str">
+        <x:v>POSCD @ 127.0.0.1:11000</x:v>
       </x:c>
       <x:c r="I25"/>
       <x:c r="J25"/>
     </x:row>
     <x:row r="26" ht="17.25" customHeight="1">
-      <x:c r="A26" s="70" t="str">
-        <x:v>5. Filler B</x:v>
-      </x:c>
-      <x:c r="B26" s="71"/>
-      <x:c r="C26" s="71"/>
-      <x:c r="D26" s="71"/>
-      <x:c r="E26" s="72"/>
+      <x:c r="A26" s="104" t="str">
+        <x:v>Signal</x:v>
+      </x:c>
+      <x:c r="B26" s="104" t="str">
+        <x:v>Direction</x:v>
+      </x:c>
+      <x:c r="C26" s="104" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="D26" s="104" t="str">
+        <x:v>Receiver Port</x:v>
+      </x:c>
+      <x:c r="E26" s="104" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
       <x:c r="F26" s="62"/>
-      <x:c r="G26" s="54" t="str">
-        <x:v>Capper</x:v>
-      </x:c>
-      <x:c r="H26" s="55" t="str">
-        <x:v>CapperControllerCD @ 127.0.0.1:11007</x:v>
+      <x:c r="G26" s="118" t="str">
+        <x:v>ABS Coordinator</x:v>
+      </x:c>
+      <x:c r="H26" s="119" t="str">
+        <x:v>CoordinatorCD @ 127.0.0.1:11001</x:v>
       </x:c>
       <x:c r="I26"/>
       <x:c r="J26"/>
     </x:row>
     <x:row r="27" ht="17.25" customHeight="1">
-      <x:c r="A27" s="40" t="str">
-        <x:v>Signal</x:v>
-      </x:c>
-      <x:c r="B27" s="40" t="str">
-        <x:v>Direction</x:v>
-      </x:c>
-      <x:c r="C27" s="40" t="str">
-        <x:v>Type</x:v>
-      </x:c>
-      <x:c r="D27" s="40" t="str">
-        <x:v>Receiver Port</x:v>
-      </x:c>
-      <x:c r="E27" s="40" t="str">
-        <x:v>Purpose</x:v>
+      <x:c r="A27" s="105" t="str">
+        <x:v>FILL_A_RATIO</x:v>
+      </x:c>
+      <x:c r="B27" s="105" t="str">
+        <x:v>Coordinator → Filler A</x:v>
+      </x:c>
+      <x:c r="C27" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D27" s="106" t="n">
+        <x:v>11004</x:v>
+      </x:c>
+      <x:c r="E27" s="105" t="str">
+        <x:v>Set Liquid A percentage (0–100)</x:v>
       </x:c>
       <x:c r="F27" s="62"/>
-      <x:c r="G27" s="54" t="str">
-        <x:v>ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="H27" s="55" t="str">
-        <x:v>ABSVisualisationPlantCD @ 127.0.0.1:11008</x:v>
+      <x:c r="G27" s="118" t="str">
+        <x:v>Bottle Loader</x:v>
+      </x:c>
+      <x:c r="H27" s="119" t="str">
+        <x:v>BottleLoaderControllerCD @ 127.0.0.1:11002</x:v>
       </x:c>
       <x:c r="I27"/>
       <x:c r="J27"/>
     </x:row>
     <x:row r="28" ht="17.25" customHeight="1">
-      <x:c r="A28" s="41" t="str">
-        <x:v>FILL_B_RATIO</x:v>
-      </x:c>
-      <x:c r="B28" s="41" t="str">
-        <x:v>Coordinator → Filler B</x:v>
-      </x:c>
-      <x:c r="C28" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D28" s="42" t="n">
-        <x:v>11005</x:v>
-      </x:c>
-      <x:c r="E28" s="41" t="str">
-        <x:v>Set Liquid B percentage (0–100)</x:v>
+      <x:c r="A28" s="105" t="str">
+        <x:v>FILLER_A_STATUS_REQUEST</x:v>
+      </x:c>
+      <x:c r="B28" s="105" t="str">
+        <x:v>Coordinator → Filler A</x:v>
+      </x:c>
+      <x:c r="C28" s="105" t="str">
+        <x:v>pure signal</x:v>
+      </x:c>
+      <x:c r="D28" s="106" t="n">
+        <x:v>11004</x:v>
+      </x:c>
+      <x:c r="E28" s="105" t="str">
+        <x:v>Request current status</x:v>
       </x:c>
       <x:c r="F28" s="62"/>
-      <x:c r="G28" s="62"/>
-      <x:c r="H28" s="62"/>
+      <x:c r="G28" s="118" t="str">
+        <x:v>Conveyor</x:v>
+      </x:c>
+      <x:c r="H28" s="119" t="str">
+        <x:v>ConveyorControllerCD @ 127.0.0.1:11003</x:v>
+      </x:c>
       <x:c r="I28"/>
       <x:c r="J28"/>
     </x:row>
     <x:row r="29" ht="17.25" customHeight="1">
-      <x:c r="A29" s="41" t="str">
-        <x:v>FILLER_B_STATUS_REQUEST</x:v>
-      </x:c>
-      <x:c r="B29" s="41" t="str">
-        <x:v>Coordinator → Filler B</x:v>
-      </x:c>
-      <x:c r="C29" s="41" t="str">
-        <x:v>pure signal</x:v>
-      </x:c>
-      <x:c r="D29" s="42" t="n">
-        <x:v>11005</x:v>
-      </x:c>
-      <x:c r="E29" s="41" t="str">
-        <x:v>Request current status</x:v>
+      <x:c r="A29" s="105" t="str">
+        <x:v>FILLER_A_STATUS</x:v>
+      </x:c>
+      <x:c r="B29" s="105" t="str">
+        <x:v>Filler A → Coordinator</x:v>
+      </x:c>
+      <x:c r="C29" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D29" s="106" t="n">
+        <x:v>11001</x:v>
+      </x:c>
+      <x:c r="E29" s="105" t="str">
+        <x:v>Return current status code</x:v>
       </x:c>
       <x:c r="F29" s="62"/>
-      <x:c r="G29" s="68" t="str">
-        <x:v>Test Mapping Boundary</x:v>
-      </x:c>
-      <x:c r="H29" s="69"/>
+      <x:c r="G29" s="118" t="str">
+        <x:v>Filler A</x:v>
+      </x:c>
+      <x:c r="H29" s="119" t="str">
+        <x:v>FillerAControllerCD @ 127.0.0.1:11004</x:v>
+      </x:c>
       <x:c r="I29"/>
       <x:c r="J29"/>
     </x:row>
-    <x:row r="30" ht="43.5" customHeight="1">
-      <x:c r="A30" s="41" t="str">
-        <x:v>FILLER_B_STATUS</x:v>
-      </x:c>
-      <x:c r="B30" s="41" t="str">
-        <x:v>Filler B → Coordinator</x:v>
-      </x:c>
-      <x:c r="C30" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D30" s="42" t="n">
-        <x:v>11001</x:v>
-      </x:c>
-      <x:c r="E30" s="41" t="str">
-        <x:v>Return current status code</x:v>
-      </x:c>
+    <x:row r="30" ht="17.25" customHeight="1">
+      <x:c r="A30" s="62"/>
+      <x:c r="B30" s="62"/>
+      <x:c r="C30" s="62"/>
+      <x:c r="D30" s="62"/>
+      <x:c r="E30" s="62"/>
       <x:c r="F30" s="62"/>
-      <x:c r="G30" s="54" t="str">
-        <x:v>MockControllerCD</x:v>
-      </x:c>
-      <x:c r="H30" s="55" t="str">
-        <x:v>tests/ XML maps all machine-facing inputs to port 11002 for integration testing only.</x:v>
+      <x:c r="G30" s="118" t="str">
+        <x:v>Filler B</x:v>
+      </x:c>
+      <x:c r="H30" s="119" t="str">
+        <x:v>FillerBControllerCD @ 127.0.0.1:11005</x:v>
       </x:c>
       <x:c r="I30"/>
       <x:c r="J30"/>
     </x:row>
-    <x:row r="31" ht="43.5" customHeight="1">
-      <x:c r="A31" s="62"/>
-      <x:c r="B31" s="62"/>
-      <x:c r="C31" s="62"/>
-      <x:c r="D31" s="62"/>
-      <x:c r="E31" s="62"/>
+    <x:row r="31" ht="17.25" customHeight="1">
+      <x:c r="A31" s="133" t="str">
+        <x:v>6. Filler B Controller</x:v>
+      </x:c>
+      <x:c r="B31" s="134"/>
+      <x:c r="C31" s="134"/>
+      <x:c r="D31" s="134"/>
+      <x:c r="E31" s="135"/>
       <x:c r="F31" s="62"/>
-      <x:c r="G31" s="54" t="str">
-        <x:v>Production</x:v>
-      </x:c>
-      <x:c r="H31" s="55" t="str">
-        <x:v>Use the separate Controller Clock Domains and ports 11002–11007 shown above.</x:v>
+      <x:c r="G31" s="118" t="str">
+        <x:v>Lid Loader</x:v>
+      </x:c>
+      <x:c r="H31" s="119" t="str">
+        <x:v>LidLoaderControllerCD @ 127.0.0.1:11006</x:v>
       </x:c>
       <x:c r="I31"/>
       <x:c r="J31"/>
     </x:row>
-    <x:row r="32" ht="43.5" customHeight="1">
-      <x:c r="A32" s="70" t="str">
-        <x:v>6. Lid Loader</x:v>
-      </x:c>
-      <x:c r="B32" s="71"/>
-      <x:c r="C32" s="71"/>
-      <x:c r="D32" s="71"/>
-      <x:c r="E32" s="72"/>
+    <x:row r="32" ht="17.25" customHeight="1">
+      <x:c r="A32" s="104" t="str">
+        <x:v>Signal</x:v>
+      </x:c>
+      <x:c r="B32" s="104" t="str">
+        <x:v>Direction</x:v>
+      </x:c>
+      <x:c r="C32" s="104" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="D32" s="104" t="str">
+        <x:v>Receiver Port</x:v>
+      </x:c>
+      <x:c r="E32" s="104" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
       <x:c r="F32" s="62"/>
-      <x:c r="G32" s="54" t="str">
-        <x:v>Real machines</x:v>
-      </x:c>
-      <x:c r="H32" s="55" t="str">
-        <x:v>Machine Controller/Plant implementations are not yet present in machines/; this workbook records the frozen Coordinator-facing contract.</x:v>
+      <x:c r="G32" s="118" t="str">
+        <x:v>Capper</x:v>
+      </x:c>
+      <x:c r="H32" s="119" t="str">
+        <x:v>CapperControllerCD @ 127.0.0.1:11007</x:v>
       </x:c>
       <x:c r="I32"/>
       <x:c r="J32"/>
     </x:row>
     <x:row r="33" ht="17.25" customHeight="1">
-      <x:c r="A33" s="40" t="str">
-        <x:v>Signal</x:v>
-      </x:c>
-      <x:c r="B33" s="40" t="str">
-        <x:v>Direction</x:v>
-      </x:c>
-      <x:c r="C33" s="40" t="str">
-        <x:v>Type</x:v>
-      </x:c>
-      <x:c r="D33" s="40" t="str">
-        <x:v>Receiver Port</x:v>
-      </x:c>
-      <x:c r="E33" s="40" t="str">
-        <x:v>Purpose</x:v>
+      <x:c r="A33" s="105" t="str">
+        <x:v>FILL_B_RATIO</x:v>
+      </x:c>
+      <x:c r="B33" s="105" t="str">
+        <x:v>Coordinator → Filler B</x:v>
+      </x:c>
+      <x:c r="C33" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D33" s="106" t="n">
+        <x:v>11005</x:v>
+      </x:c>
+      <x:c r="E33" s="105" t="str">
+        <x:v>Set Liquid B percentage (0–100)</x:v>
       </x:c>
       <x:c r="F33" s="62"/>
-      <x:c r="G33" s="62"/>
-      <x:c r="H33" s="62"/>
+      <x:c r="G33" s="118" t="str">
+        <x:v>ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="H33" s="119" t="str">
+        <x:v>ABSVisualisationPlantCD @ 127.0.0.1:11008</x:v>
+      </x:c>
       <x:c r="I33"/>
       <x:c r="J33"/>
     </x:row>
     <x:row r="34" ht="17.25" customHeight="1">
-      <x:c r="A34" s="41" t="str">
-        <x:v>LID_STATUS_REQUEST</x:v>
-      </x:c>
-      <x:c r="B34" s="41" t="str">
-        <x:v>Coordinator → Lid Loader</x:v>
-      </x:c>
-      <x:c r="C34" s="41" t="str">
+      <x:c r="A34" s="105" t="str">
+        <x:v>FILLER_B_STATUS_REQUEST</x:v>
+      </x:c>
+      <x:c r="B34" s="105" t="str">
+        <x:v>Coordinator → Filler B</x:v>
+      </x:c>
+      <x:c r="C34" s="105" t="str">
         <x:v>pure signal</x:v>
       </x:c>
-      <x:c r="D34" s="42" t="n">
-        <x:v>11006</x:v>
-      </x:c>
-      <x:c r="E34" s="41" t="str">
+      <x:c r="D34" s="106" t="n">
+        <x:v>11005</x:v>
+      </x:c>
+      <x:c r="E34" s="105" t="str">
         <x:v>Request current status</x:v>
       </x:c>
       <x:c r="F34" s="62"/>
-      <x:c r="G34" s="62"/>
-      <x:c r="H34" s="62"/>
+      <x:c r="G34" s="118" t="str">
+        <x:v>Rotary Turntable</x:v>
+      </x:c>
+      <x:c r="H34" s="119" t="str">
+        <x:v>RotaryTurntableControllerCD @ 127.0.0.1:11009</x:v>
+      </x:c>
       <x:c r="I34"/>
       <x:c r="J34"/>
     </x:row>
     <x:row r="35" ht="17.25" customHeight="1">
-      <x:c r="A35" s="41" t="str">
-        <x:v>LID_STATUS</x:v>
-      </x:c>
-      <x:c r="B35" s="41" t="str">
-        <x:v>Lid Loader → Coordinator</x:v>
-      </x:c>
-      <x:c r="C35" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D35" s="42" t="n">
+      <x:c r="A35" s="105" t="str">
+        <x:v>FILLER_B_STATUS</x:v>
+      </x:c>
+      <x:c r="B35" s="105" t="str">
+        <x:v>Filler B → Coordinator</x:v>
+      </x:c>
+      <x:c r="C35" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D35" s="106" t="n">
         <x:v>11001</x:v>
       </x:c>
-      <x:c r="E35" s="41" t="str">
+      <x:c r="E35" s="105" t="str">
         <x:v>Return current status code</x:v>
       </x:c>
       <x:c r="F35" s="62"/>
-      <x:c r="G35" s="62"/>
-      <x:c r="H35" s="62"/>
+      <x:c r="G35" s="118" t="str">
+        <x:v>Bottle Unloader</x:v>
+      </x:c>
+      <x:c r="H35" s="119" t="str">
+        <x:v>BottleUnloaderControllerCD @ 127.0.0.1:11010</x:v>
+      </x:c>
       <x:c r="I35"/>
       <x:c r="J35"/>
     </x:row>
@@ -1398,101 +1601,105 @@
       <x:c r="J36"/>
     </x:row>
     <x:row r="37" ht="17.25" customHeight="1">
-      <x:c r="A37" s="70" t="str">
-        <x:v>7. Capper</x:v>
-      </x:c>
-      <x:c r="B37" s="71"/>
-      <x:c r="C37" s="71"/>
-      <x:c r="D37" s="71"/>
-      <x:c r="E37" s="72"/>
+      <x:c r="A37" s="133" t="str">
+        <x:v>7. Lid Loader Controller</x:v>
+      </x:c>
+      <x:c r="B37" s="134"/>
+      <x:c r="C37" s="134"/>
+      <x:c r="D37" s="134"/>
+      <x:c r="E37" s="135"/>
       <x:c r="F37" s="62"/>
-      <x:c r="G37" s="62"/>
-      <x:c r="H37" s="62"/>
+      <x:c r="G37" s="131" t="str">
+        <x:v>Test Mapping Boundary</x:v>
+      </x:c>
+      <x:c r="H37" s="132"/>
       <x:c r="I37"/>
       <x:c r="J37"/>
     </x:row>
-    <x:row r="38" ht="17.25" customHeight="1">
-      <x:c r="A38" s="40" t="str">
+    <x:row r="38" ht="41.25" customHeight="1">
+      <x:c r="A38" s="104" t="str">
         <x:v>Signal</x:v>
       </x:c>
-      <x:c r="B38" s="40" t="str">
+      <x:c r="B38" s="104" t="str">
         <x:v>Direction</x:v>
       </x:c>
-      <x:c r="C38" s="40" t="str">
+      <x:c r="C38" s="104" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D38" s="40" t="str">
+      <x:c r="D38" s="104" t="str">
         <x:v>Receiver Port</x:v>
       </x:c>
-      <x:c r="E38" s="40" t="str">
+      <x:c r="E38" s="104" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="F38" s="62"/>
-      <x:c r="G38" s="62"/>
-      <x:c r="H38" s="62"/>
+      <x:c r="G38" s="118" t="str">
+        <x:v>MockControllerCD</x:v>
+      </x:c>
+      <x:c r="H38" s="119" t="str">
+        <x:v>TEST ONLY: all machine-facing inputs are mapped to port 11002.</x:v>
+      </x:c>
       <x:c r="I38"/>
       <x:c r="J38"/>
     </x:row>
-    <x:row r="39" ht="17.25" customHeight="1">
-      <x:c r="A39" s="41" t="str">
-        <x:v>CAPPER_STATUS_REQUEST</x:v>
-      </x:c>
-      <x:c r="B39" s="41" t="str">
-        <x:v>Coordinator → Capper</x:v>
-      </x:c>
-      <x:c r="C39" s="41" t="str">
+    <x:row r="39" ht="41.25" customHeight="1">
+      <x:c r="A39" s="105" t="str">
+        <x:v>LID_STATUS_REQUEST</x:v>
+      </x:c>
+      <x:c r="B39" s="105" t="str">
+        <x:v>Coordinator → Lid Loader</x:v>
+      </x:c>
+      <x:c r="C39" s="105" t="str">
         <x:v>pure signal</x:v>
       </x:c>
-      <x:c r="D39" s="42" t="n">
-        <x:v>11007</x:v>
-      </x:c>
-      <x:c r="E39" s="41" t="str">
+      <x:c r="D39" s="106" t="n">
+        <x:v>11006</x:v>
+      </x:c>
+      <x:c r="E39" s="105" t="str">
         <x:v>Request current status</x:v>
       </x:c>
       <x:c r="F39" s="62"/>
-      <x:c r="G39" s="62"/>
-      <x:c r="H39" s="62"/>
+      <x:c r="G39" s="118" t="str">
+        <x:v>Production</x:v>
+      </x:c>
+      <x:c r="H39" s="119" t="str">
+        <x:v>Use the separate Clock Domains and ports 11002–11010 shown above.</x:v>
+      </x:c>
       <x:c r="I39"/>
       <x:c r="J39"/>
     </x:row>
-    <x:row r="40" ht="17.25" customHeight="1">
-      <x:c r="A40" s="41" t="str">
-        <x:v>CAPPER_STATUS</x:v>
-      </x:c>
-      <x:c r="B40" s="41" t="str">
-        <x:v>Capper → Coordinator</x:v>
-      </x:c>
-      <x:c r="C40" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D40" s="42" t="n">
+    <x:row r="40" ht="41.25" customHeight="1">
+      <x:c r="A40" s="105" t="str">
+        <x:v>LID_STATUS</x:v>
+      </x:c>
+      <x:c r="B40" s="105" t="str">
+        <x:v>Lid Loader → Coordinator</x:v>
+      </x:c>
+      <x:c r="C40" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D40" s="106" t="n">
         <x:v>11001</x:v>
       </x:c>
-      <x:c r="E40" s="41" t="str">
+      <x:c r="E40" s="105" t="str">
         <x:v>Return current status code</x:v>
       </x:c>
       <x:c r="F40" s="62"/>
-      <x:c r="G40" s="62"/>
-      <x:c r="H40" s="62"/>
+      <x:c r="G40" s="118" t="str">
+        <x:v>Real machines</x:v>
+      </x:c>
+      <x:c r="H40" s="119" t="str">
+        <x:v>Machine Controller/Plant implementations are not yet present; this workbook defines their Coordinator-facing contract.</x:v>
+      </x:c>
       <x:c r="I40"/>
       <x:c r="J40"/>
     </x:row>
     <x:row r="41" ht="17.25" customHeight="1">
-      <x:c r="A41" s="41" t="str">
-        <x:v>BOTTLE_DONE</x:v>
-      </x:c>
-      <x:c r="B41" s="41" t="str">
-        <x:v>Capper → Coordinator</x:v>
-      </x:c>
-      <x:c r="C41" s="41" t="str">
-        <x:v>pure signal</x:v>
-      </x:c>
-      <x:c r="D41" s="42" t="n">
-        <x:v>11001</x:v>
-      </x:c>
-      <x:c r="E41" s="41" t="str">
-        <x:v>One bottle completed the full line</x:v>
-      </x:c>
+      <x:c r="A41" s="62"/>
+      <x:c r="B41" s="62"/>
+      <x:c r="C41" s="62"/>
+      <x:c r="D41" s="62"/>
+      <x:c r="E41" s="62"/>
       <x:c r="F41" s="62"/>
       <x:c r="G41" s="62"/>
       <x:c r="H41" s="62"/>
@@ -1500,11 +1707,13 @@
       <x:c r="J41"/>
     </x:row>
     <x:row r="42" ht="17.25" customHeight="1">
-      <x:c r="A42" s="62"/>
-      <x:c r="B42" s="62"/>
-      <x:c r="C42" s="62"/>
-      <x:c r="D42" s="62"/>
-      <x:c r="E42" s="62"/>
+      <x:c r="A42" s="133" t="str">
+        <x:v>8. Capper Controller</x:v>
+      </x:c>
+      <x:c r="B42" s="134"/>
+      <x:c r="C42" s="134"/>
+      <x:c r="D42" s="134"/>
+      <x:c r="E42" s="135"/>
       <x:c r="F42" s="62"/>
       <x:c r="G42" s="62"/>
       <x:c r="H42" s="62"/>
@@ -1512,13 +1721,21 @@
       <x:c r="J42"/>
     </x:row>
     <x:row r="43" ht="17.25" customHeight="1">
-      <x:c r="A43" s="70" t="str">
-        <x:v>8. ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="B43" s="71"/>
-      <x:c r="C43" s="71"/>
-      <x:c r="D43" s="71"/>
-      <x:c r="E43" s="72"/>
+      <x:c r="A43" s="104" t="str">
+        <x:v>Signal</x:v>
+      </x:c>
+      <x:c r="B43" s="104" t="str">
+        <x:v>Direction</x:v>
+      </x:c>
+      <x:c r="C43" s="104" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="D43" s="104" t="str">
+        <x:v>Receiver Port</x:v>
+      </x:c>
+      <x:c r="E43" s="104" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
       <x:c r="F43" s="62"/>
       <x:c r="G43" s="62"/>
       <x:c r="H43" s="62"/>
@@ -1526,20 +1743,20 @@
       <x:c r="J43"/>
     </x:row>
     <x:row r="44" ht="17.25" customHeight="1">
-      <x:c r="A44" s="40" t="str">
-        <x:v>Signal</x:v>
-      </x:c>
-      <x:c r="B44" s="40" t="str">
-        <x:v>Direction</x:v>
-      </x:c>
-      <x:c r="C44" s="40" t="str">
-        <x:v>Type</x:v>
-      </x:c>
-      <x:c r="D44" s="40" t="str">
-        <x:v>Receiver Port</x:v>
-      </x:c>
-      <x:c r="E44" s="40" t="str">
-        <x:v>Purpose</x:v>
+      <x:c r="A44" s="105" t="str">
+        <x:v>CAPPER_STATUS_REQUEST</x:v>
+      </x:c>
+      <x:c r="B44" s="105" t="str">
+        <x:v>Coordinator → Capper</x:v>
+      </x:c>
+      <x:c r="C44" s="105" t="str">
+        <x:v>pure signal</x:v>
+      </x:c>
+      <x:c r="D44" s="106" t="n">
+        <x:v>11007</x:v>
+      </x:c>
+      <x:c r="E44" s="105" t="str">
+        <x:v>Request current status</x:v>
       </x:c>
       <x:c r="F44" s="62"/>
       <x:c r="G44" s="62"/>
@@ -1548,20 +1765,20 @@
       <x:c r="J44"/>
     </x:row>
     <x:row r="45" ht="17.25" customHeight="1">
-      <x:c r="A45" s="41" t="str">
-        <x:v>VIZ_LOADER_STATUS</x:v>
-      </x:c>
-      <x:c r="B45" s="41" t="str">
-        <x:v>Coordinator → ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="C45" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D45" s="42" t="n">
-        <x:v>11008</x:v>
-      </x:c>
-      <x:c r="E45" s="41" t="str">
-        <x:v>Display latest Loader status</x:v>
+      <x:c r="A45" s="105" t="str">
+        <x:v>CAPPER_STATUS</x:v>
+      </x:c>
+      <x:c r="B45" s="105" t="str">
+        <x:v>Capper → Coordinator</x:v>
+      </x:c>
+      <x:c r="C45" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D45" s="106" t="n">
+        <x:v>11001</x:v>
+      </x:c>
+      <x:c r="E45" s="105" t="str">
+        <x:v>Return current status code</x:v>
       </x:c>
       <x:c r="F45" s="62"/>
       <x:c r="G45" s="62"/>
@@ -1570,21 +1787,11 @@
       <x:c r="J45"/>
     </x:row>
     <x:row r="46" ht="17.25" customHeight="1">
-      <x:c r="A46" s="41" t="str">
-        <x:v>VIZ_TRANSPORT_STATUS</x:v>
-      </x:c>
-      <x:c r="B46" s="41" t="str">
-        <x:v>Coordinator → ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="C46" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D46" s="42" t="n">
-        <x:v>11008</x:v>
-      </x:c>
-      <x:c r="E46" s="41" t="str">
-        <x:v>Display latest Transport status</x:v>
-      </x:c>
+      <x:c r="A46" s="62"/>
+      <x:c r="B46" s="62"/>
+      <x:c r="C46" s="62"/>
+      <x:c r="D46" s="62"/>
+      <x:c r="E46" s="62"/>
       <x:c r="F46" s="62"/>
       <x:c r="G46" s="62"/>
       <x:c r="H46" s="62"/>
@@ -1592,21 +1799,13 @@
       <x:c r="J46"/>
     </x:row>
     <x:row r="47" ht="17.25" customHeight="1">
-      <x:c r="A47" s="41" t="str">
-        <x:v>VIZ_FILLER_A_STATUS</x:v>
-      </x:c>
-      <x:c r="B47" s="41" t="str">
-        <x:v>Coordinator → ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="C47" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D47" s="42" t="n">
-        <x:v>11008</x:v>
-      </x:c>
-      <x:c r="E47" s="41" t="str">
-        <x:v>Display latest Filler A status</x:v>
-      </x:c>
+      <x:c r="A47" s="133" t="str">
+        <x:v>9. Bottle Unloader Controller</x:v>
+      </x:c>
+      <x:c r="B47" s="134"/>
+      <x:c r="C47" s="134"/>
+      <x:c r="D47" s="134"/>
+      <x:c r="E47" s="135"/>
       <x:c r="F47" s="62"/>
       <x:c r="G47" s="62"/>
       <x:c r="H47" s="62"/>
@@ -1614,20 +1813,20 @@
       <x:c r="J47"/>
     </x:row>
     <x:row r="48" ht="17.25" customHeight="1">
-      <x:c r="A48" s="41" t="str">
-        <x:v>VIZ_FILLER_B_STATUS</x:v>
-      </x:c>
-      <x:c r="B48" s="41" t="str">
-        <x:v>Coordinator → ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="C48" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D48" s="42" t="n">
-        <x:v>11008</x:v>
-      </x:c>
-      <x:c r="E48" s="41" t="str">
-        <x:v>Display latest Filler B status</x:v>
+      <x:c r="A48" s="104" t="str">
+        <x:v>Signal</x:v>
+      </x:c>
+      <x:c r="B48" s="104" t="str">
+        <x:v>Direction</x:v>
+      </x:c>
+      <x:c r="C48" s="104" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="D48" s="104" t="str">
+        <x:v>Receiver Port</x:v>
+      </x:c>
+      <x:c r="E48" s="104" t="str">
+        <x:v>Purpose</x:v>
       </x:c>
       <x:c r="F48" s="62"/>
       <x:c r="G48" s="62"/>
@@ -1636,20 +1835,20 @@
       <x:c r="J48"/>
     </x:row>
     <x:row r="49" ht="17.25" customHeight="1">
-      <x:c r="A49" s="41" t="str">
-        <x:v>VIZ_LID_STATUS</x:v>
-      </x:c>
-      <x:c r="B49" s="41" t="str">
-        <x:v>Coordinator → ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="C49" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D49" s="42" t="n">
-        <x:v>11008</x:v>
-      </x:c>
-      <x:c r="E49" s="41" t="str">
-        <x:v>Display latest Lid Loader status</x:v>
+      <x:c r="A49" s="105" t="str">
+        <x:v>UNLOADER_STATUS_REQUEST</x:v>
+      </x:c>
+      <x:c r="B49" s="105" t="str">
+        <x:v>Coordinator → Bottle Unloader</x:v>
+      </x:c>
+      <x:c r="C49" s="105" t="str">
+        <x:v>pure signal</x:v>
+      </x:c>
+      <x:c r="D49" s="106" t="n">
+        <x:v>11010</x:v>
+      </x:c>
+      <x:c r="E49" s="105" t="str">
+        <x:v>Request current status</x:v>
       </x:c>
       <x:c r="F49" s="62"/>
       <x:c r="G49" s="62"/>
@@ -1658,20 +1857,20 @@
       <x:c r="J49"/>
     </x:row>
     <x:row r="50" ht="17.25" customHeight="1">
-      <x:c r="A50" s="41" t="str">
-        <x:v>VIZ_CAPPER_STATUS</x:v>
-      </x:c>
-      <x:c r="B50" s="41" t="str">
-        <x:v>Coordinator → ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="C50" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D50" s="42" t="n">
-        <x:v>11008</x:v>
-      </x:c>
-      <x:c r="E50" s="41" t="str">
-        <x:v>Display latest Capper status</x:v>
+      <x:c r="A50" s="105" t="str">
+        <x:v>UNLOADER_STATUS</x:v>
+      </x:c>
+      <x:c r="B50" s="105" t="str">
+        <x:v>Bottle Unloader → Coordinator</x:v>
+      </x:c>
+      <x:c r="C50" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D50" s="106" t="n">
+        <x:v>11001</x:v>
+      </x:c>
+      <x:c r="E50" s="105" t="str">
+        <x:v>Return current status code</x:v>
       </x:c>
       <x:c r="F50" s="62"/>
       <x:c r="G50" s="62"/>
@@ -1680,20 +1879,20 @@
       <x:c r="J50"/>
     </x:row>
     <x:row r="51" ht="17.25" customHeight="1">
-      <x:c r="A51" s="41" t="str">
-        <x:v>VIZ_REQUIRED_BOTTLES</x:v>
-      </x:c>
-      <x:c r="B51" s="41" t="str">
-        <x:v>Coordinator → ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="C51" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D51" s="42" t="n">
-        <x:v>11008</x:v>
-      </x:c>
-      <x:c r="E51" s="41" t="str">
-        <x:v>Display current batch target</x:v>
+      <x:c r="A51" s="105" t="str">
+        <x:v>BOTTLE_DONE</x:v>
+      </x:c>
+      <x:c r="B51" s="105" t="str">
+        <x:v>Bottle Unloader → Coordinator</x:v>
+      </x:c>
+      <x:c r="C51" s="105" t="str">
+        <x:v>pure signal</x:v>
+      </x:c>
+      <x:c r="D51" s="106" t="n">
+        <x:v>11001</x:v>
+      </x:c>
+      <x:c r="E51" s="105" t="str">
+        <x:v>One finished bottle collected</x:v>
       </x:c>
       <x:c r="F51" s="62"/>
       <x:c r="G51" s="62"/>
@@ -1702,21 +1901,11 @@
       <x:c r="J51"/>
     </x:row>
     <x:row r="52" ht="17.25" customHeight="1">
-      <x:c r="A52" s="41" t="str">
-        <x:v>VIZ_COMPLETED_BOTTLES</x:v>
-      </x:c>
-      <x:c r="B52" s="41" t="str">
-        <x:v>Coordinator → ABS Visualisation</x:v>
-      </x:c>
-      <x:c r="C52" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D52" s="42" t="n">
-        <x:v>11008</x:v>
-      </x:c>
-      <x:c r="E52" s="41" t="str">
-        <x:v>Display current batch progress</x:v>
-      </x:c>
+      <x:c r="A52" s="62"/>
+      <x:c r="B52" s="62"/>
+      <x:c r="C52" s="62"/>
+      <x:c r="D52" s="62"/>
+      <x:c r="E52" s="62"/>
       <x:c r="F52" s="62"/>
       <x:c r="G52" s="62"/>
       <x:c r="H52" s="62"/>
@@ -1724,11 +1913,13 @@
       <x:c r="J52"/>
     </x:row>
     <x:row r="53" ht="17.25" customHeight="1">
-      <x:c r="A53" s="62"/>
-      <x:c r="B53" s="62"/>
-      <x:c r="C53" s="62"/>
-      <x:c r="D53" s="62"/>
-      <x:c r="E53" s="62"/>
+      <x:c r="A53" s="133" t="str">
+        <x:v>10. ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="B53" s="134"/>
+      <x:c r="C53" s="134"/>
+      <x:c r="D53" s="134"/>
+      <x:c r="E53" s="135"/>
       <x:c r="F53" s="62"/>
       <x:c r="G53" s="62"/>
       <x:c r="H53" s="62"/>
@@ -1736,148 +1927,378 @@
       <x:c r="J53"/>
     </x:row>
     <x:row r="54" ht="17.25" customHeight="1">
-      <x:c r="A54" s="70" t="str">
-        <x:v>9. Status Codes</x:v>
-      </x:c>
-      <x:c r="B54" s="71"/>
-      <x:c r="C54" s="71"/>
-      <x:c r="D54" s="71"/>
-      <x:c r="E54" s="72"/>
+      <x:c r="A54" s="104" t="str">
+        <x:v>Signal</x:v>
+      </x:c>
+      <x:c r="B54" s="104" t="str">
+        <x:v>Direction</x:v>
+      </x:c>
+      <x:c r="C54" s="104" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="D54" s="104" t="str">
+        <x:v>Receiver Port</x:v>
+      </x:c>
+      <x:c r="E54" s="104" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
       <x:c r="F54" s="62"/>
       <x:c r="G54" s="62"/>
       <x:c r="H54" s="62"/>
     </x:row>
     <x:row r="55" ht="17.25" customHeight="1">
-      <x:c r="A55" s="40" t="str">
-        <x:v>Signal</x:v>
-      </x:c>
-      <x:c r="B55" s="40" t="str">
-        <x:v>Direction</x:v>
-      </x:c>
-      <x:c r="C55" s="40" t="str">
-        <x:v>Type</x:v>
-      </x:c>
-      <x:c r="D55" s="40" t="str">
-        <x:v>Receiver Port</x:v>
-      </x:c>
-      <x:c r="E55" s="40" t="str">
-        <x:v>Purpose</x:v>
+      <x:c r="A55" s="105" t="str">
+        <x:v>VIZ_LOADER_STATUS</x:v>
+      </x:c>
+      <x:c r="B55" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C55" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D55" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E55" s="105" t="str">
+        <x:v>Display latest Loader status</x:v>
       </x:c>
       <x:c r="F55" s="62"/>
       <x:c r="G55" s="62"/>
       <x:c r="H55" s="62"/>
     </x:row>
     <x:row r="56" ht="17.25" customHeight="1">
-      <x:c r="A56" s="42" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B56" s="41" t="str">
-        <x:v>Controller status / VIZ status</x:v>
-      </x:c>
-      <x:c r="C56" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D56" s="42" t="str">
-        <x:v>11001 / 11008</x:v>
-      </x:c>
-      <x:c r="E56" s="41" t="str">
-        <x:v>IDLE — no active work</x:v>
+      <x:c r="A56" s="105" t="str">
+        <x:v>VIZ_CONVEYOR_STATUS</x:v>
+      </x:c>
+      <x:c r="B56" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C56" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D56" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E56" s="105" t="str">
+        <x:v>Display latest Conveyor status</x:v>
       </x:c>
       <x:c r="F56" s="62"/>
       <x:c r="G56" s="62"/>
       <x:c r="H56" s="62"/>
     </x:row>
     <x:row r="57" ht="17.25" customHeight="1">
-      <x:c r="A57" s="42" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B57" s="41" t="str">
-        <x:v>Controller status / VIZ status</x:v>
-      </x:c>
-      <x:c r="C57" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D57" s="42" t="str">
-        <x:v>11001 / 11008</x:v>
-      </x:c>
-      <x:c r="E57" s="41" t="str">
-        <x:v>READY — ready for work</x:v>
+      <x:c r="A57" s="105" t="str">
+        <x:v>VIZ_ROTARY_STATUS</x:v>
+      </x:c>
+      <x:c r="B57" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C57" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D57" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E57" s="105" t="str">
+        <x:v>Display latest Rotary status</x:v>
       </x:c>
       <x:c r="F57" s="62"/>
       <x:c r="G57" s="62"/>
       <x:c r="H57" s="62"/>
     </x:row>
     <x:row r="58" ht="17.25" customHeight="1">
-      <x:c r="A58" s="42" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B58" s="41" t="str">
-        <x:v>Controller status / VIZ status</x:v>
-      </x:c>
-      <x:c r="C58" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D58" s="42" t="str">
-        <x:v>11001 / 11008</x:v>
-      </x:c>
-      <x:c r="E58" s="41" t="str">
-        <x:v>BUSY — processing</x:v>
+      <x:c r="A58" s="105" t="str">
+        <x:v>VIZ_FILLER_A_STATUS</x:v>
+      </x:c>
+      <x:c r="B58" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C58" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D58" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E58" s="105" t="str">
+        <x:v>Display latest Filler A status</x:v>
       </x:c>
       <x:c r="F58" s="62"/>
       <x:c r="G58" s="62"/>
       <x:c r="H58" s="62"/>
     </x:row>
     <x:row r="59" ht="17.25" customHeight="1">
-      <x:c r="A59" s="42" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B59" s="41" t="str">
-        <x:v>Controller status / VIZ status</x:v>
-      </x:c>
-      <x:c r="C59" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D59" s="42" t="str">
-        <x:v>11001 / 11008</x:v>
-      </x:c>
-      <x:c r="E59" s="41" t="str">
-        <x:v>DONE — operation completed</x:v>
+      <x:c r="A59" s="105" t="str">
+        <x:v>VIZ_FILLER_B_STATUS</x:v>
+      </x:c>
+      <x:c r="B59" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C59" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D59" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E59" s="105" t="str">
+        <x:v>Display latest Filler B status</x:v>
       </x:c>
       <x:c r="F59" s="62"/>
       <x:c r="G59" s="62"/>
       <x:c r="H59" s="62"/>
     </x:row>
     <x:row r="60" ht="17.25" customHeight="1">
-      <x:c r="A60" s="42" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B60" s="41" t="str">
-        <x:v>Controller status / VIZ status</x:v>
-      </x:c>
-      <x:c r="C60" s="41" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="D60" s="42" t="str">
-        <x:v>11001 / 11008</x:v>
-      </x:c>
-      <x:c r="E60" s="41" t="str">
-        <x:v>FAULT — fault detected</x:v>
+      <x:c r="A60" s="105" t="str">
+        <x:v>VIZ_LID_STATUS</x:v>
+      </x:c>
+      <x:c r="B60" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C60" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D60" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E60" s="105" t="str">
+        <x:v>Display latest Lid Loader status</x:v>
       </x:c>
       <x:c r="F60" s="62"/>
       <x:c r="G60" s="62"/>
       <x:c r="H60" s="62"/>
     </x:row>
-    <x:row r="61" ht="27" customHeight="1">
-      <x:c r="A61" s="45" t="str">
-        <x:v>WAITING is a GUI-only initial label; it is not a SystemJ status value and there is no status code 5.</x:v>
-      </x:c>
-      <x:c r="B61" s="46"/>
-      <x:c r="C61" s="46"/>
-      <x:c r="D61" s="46"/>
-      <x:c r="E61" s="47"/>
+    <x:row r="61" ht="17.25" customHeight="1">
+      <x:c r="A61" s="105" t="str">
+        <x:v>VIZ_CAPPER_STATUS</x:v>
+      </x:c>
+      <x:c r="B61" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C61" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D61" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E61" s="105" t="str">
+        <x:v>Display latest Capper status</x:v>
+      </x:c>
       <x:c r="F61" s="62"/>
       <x:c r="G61" s="62"/>
       <x:c r="H61" s="62"/>
+    </x:row>
+    <x:row r="62" ht="17.25" customHeight="1">
+      <x:c r="A62" s="105" t="str">
+        <x:v>VIZ_UNLOADER_STATUS</x:v>
+      </x:c>
+      <x:c r="B62" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C62" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D62" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E62" s="105" t="str">
+        <x:v>Display latest Unloader status</x:v>
+      </x:c>
+      <x:c r="F62" s="62"/>
+      <x:c r="G62" s="62"/>
+      <x:c r="H62" s="62"/>
+    </x:row>
+    <x:row r="63" ht="17.25" customHeight="1">
+      <x:c r="A63" s="105" t="str">
+        <x:v>VIZ_REQUIRED_BOTTLES</x:v>
+      </x:c>
+      <x:c r="B63" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C63" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D63" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E63" s="105" t="str">
+        <x:v>Display current batch target</x:v>
+      </x:c>
+      <x:c r="F63" s="62"/>
+      <x:c r="G63" s="62"/>
+      <x:c r="H63" s="62"/>
+    </x:row>
+    <x:row r="64" ht="17.25" customHeight="1">
+      <x:c r="A64" s="105" t="str">
+        <x:v>VIZ_COMPLETED_BOTTLES</x:v>
+      </x:c>
+      <x:c r="B64" s="105" t="str">
+        <x:v>Coordinator → ABS Visualisation</x:v>
+      </x:c>
+      <x:c r="C64" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D64" s="106" t="n">
+        <x:v>11008</x:v>
+      </x:c>
+      <x:c r="E64" s="105" t="str">
+        <x:v>Display collected-bottle progress</x:v>
+      </x:c>
+      <x:c r="F64" s="62"/>
+      <x:c r="G64" s="62"/>
+      <x:c r="H64" s="62"/>
+    </x:row>
+    <x:row r="65" ht="17.25" customHeight="1">
+      <x:c r="A65" s="62"/>
+      <x:c r="B65" s="62"/>
+      <x:c r="C65" s="62"/>
+      <x:c r="D65" s="62"/>
+      <x:c r="E65" s="62"/>
+      <x:c r="F65" s="62"/>
+      <x:c r="G65" s="62"/>
+      <x:c r="H65" s="62"/>
+    </x:row>
+    <x:row r="66" ht="17.25" customHeight="1">
+      <x:c r="A66" s="133" t="str">
+        <x:v>11. Status Codes</x:v>
+      </x:c>
+      <x:c r="B66" s="134"/>
+      <x:c r="C66" s="134"/>
+      <x:c r="D66" s="134"/>
+      <x:c r="E66" s="135"/>
+      <x:c r="F66" s="62"/>
+      <x:c r="G66" s="62"/>
+      <x:c r="H66" s="62"/>
+    </x:row>
+    <x:row r="67" ht="17.25" customHeight="1">
+      <x:c r="A67" s="104" t="str">
+        <x:v>Signal</x:v>
+      </x:c>
+      <x:c r="B67" s="104" t="str">
+        <x:v>Direction</x:v>
+      </x:c>
+      <x:c r="C67" s="104" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="D67" s="104" t="str">
+        <x:v>Receiver Port</x:v>
+      </x:c>
+      <x:c r="E67" s="104" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
+      <x:c r="F67" s="62"/>
+      <x:c r="G67" s="62"/>
+      <x:c r="H67" s="62"/>
+    </x:row>
+    <x:row r="68" ht="17.25" customHeight="1">
+      <x:c r="A68" s="106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B68" s="105" t="str">
+        <x:v>Controller status / VIZ status</x:v>
+      </x:c>
+      <x:c r="C68" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D68" s="106" t="str">
+        <x:v>11001 / 11008</x:v>
+      </x:c>
+      <x:c r="E68" s="105" t="str">
+        <x:v>IDLE — no active work</x:v>
+      </x:c>
+      <x:c r="F68" s="62"/>
+      <x:c r="G68" s="62"/>
+      <x:c r="H68" s="62"/>
+    </x:row>
+    <x:row r="69" ht="17.25" customHeight="1">
+      <x:c r="A69" s="106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B69" s="105" t="str">
+        <x:v>Controller status / VIZ status</x:v>
+      </x:c>
+      <x:c r="C69" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D69" s="106" t="str">
+        <x:v>11001 / 11008</x:v>
+      </x:c>
+      <x:c r="E69" s="105" t="str">
+        <x:v>READY — ready for work</x:v>
+      </x:c>
+      <x:c r="F69" s="62"/>
+      <x:c r="G69" s="62"/>
+      <x:c r="H69" s="62"/>
+    </x:row>
+    <x:row r="70" ht="17.25" customHeight="1">
+      <x:c r="A70" s="106" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B70" s="105" t="str">
+        <x:v>Controller status / VIZ status</x:v>
+      </x:c>
+      <x:c r="C70" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D70" s="106" t="str">
+        <x:v>11001 / 11008</x:v>
+      </x:c>
+      <x:c r="E70" s="105" t="str">
+        <x:v>BUSY — processing</x:v>
+      </x:c>
+      <x:c r="F70" s="62"/>
+      <x:c r="G70" s="62"/>
+      <x:c r="H70" s="62"/>
+    </x:row>
+    <x:row r="71" ht="17.25" customHeight="1">
+      <x:c r="A71" s="106" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B71" s="105" t="str">
+        <x:v>Controller status / VIZ status</x:v>
+      </x:c>
+      <x:c r="C71" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D71" s="106" t="str">
+        <x:v>11001 / 11008</x:v>
+      </x:c>
+      <x:c r="E71" s="105" t="str">
+        <x:v>DONE — operation completed</x:v>
+      </x:c>
+      <x:c r="F71" s="62"/>
+      <x:c r="G71" s="62"/>
+      <x:c r="H71" s="62"/>
+    </x:row>
+    <x:row r="72" ht="17.25" customHeight="1">
+      <x:c r="A72" s="106" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B72" s="105" t="str">
+        <x:v>Controller status / VIZ status</x:v>
+      </x:c>
+      <x:c r="C72" s="105" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="D72" s="106" t="str">
+        <x:v>11001 / 11008</x:v>
+      </x:c>
+      <x:c r="E72" s="105" t="str">
+        <x:v>FAULT — fault detected</x:v>
+      </x:c>
+      <x:c r="F72" s="62"/>
+      <x:c r="G72" s="62"/>
+      <x:c r="H72" s="62"/>
+    </x:row>
+    <x:row r="73" ht="27" customHeight="1">
+      <x:c r="A73" s="109" t="str">
+        <x:v>WAITING is a GUI-only initial label; it is not a SystemJ status value and there is no status code 5.</x:v>
+      </x:c>
+      <x:c r="B73" s="110"/>
+      <x:c r="C73" s="110"/>
+      <x:c r="D73" s="110"/>
+      <x:c r="E73" s="111"/>
+      <x:c r="F73" s="62"/>
+      <x:c r="G73" s="62"/>
+      <x:c r="H73" s="62"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1887,17 +2308,20 @@
     <x:mergeCell ref="A9:E9"/>
     <x:mergeCell ref="A15:E15"/>
     <x:mergeCell ref="A20:E20"/>
-    <x:mergeCell ref="A26:E26"/>
-    <x:mergeCell ref="A32:E32"/>
+    <x:mergeCell ref="A25:E25"/>
+    <x:mergeCell ref="A31:E31"/>
     <x:mergeCell ref="A37:E37"/>
-    <x:mergeCell ref="A43:E43"/>
-    <x:mergeCell ref="A54:E54"/>
-    <x:mergeCell ref="A61:E61"/>
+    <x:mergeCell ref="A42:E42"/>
+    <x:mergeCell ref="A47:E47"/>
+    <x:mergeCell ref="A53:E53"/>
+    <x:mergeCell ref="A66:E66"/>
+    <x:mergeCell ref="A73:E73"/>
     <x:mergeCell ref="G1:H1"/>
     <x:mergeCell ref="G3:H3"/>
     <x:mergeCell ref="G8:H8"/>
-    <x:mergeCell ref="G17:H17"/>
-    <x:mergeCell ref="G29:H29"/>
+    <x:mergeCell ref="G14:H14"/>
+    <x:mergeCell ref="G23:H23"/>
+    <x:mergeCell ref="G37:H37"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
